--- a/backtest_runs/20260410_193731/by_symbol/SFL/SFL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SFL/SFL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-1900.989999999988</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>99996.36</v>
@@ -725,7 +725,7 @@
         <v>-3545.360000000003</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>96451</v>
@@ -863,7 +863,7 @@
         <v>-361.2700000000025</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>96089.73</v>
@@ -1093,7 +1093,7 @@
         <v>-356.7200000000066</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>103932.11</v>
@@ -1139,7 +1139,7 @@
         <v>-1393.209999999995</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>102538.9</v>
@@ -1277,7 +1277,7 @@
         <v>-7088.900000000009</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>95450</v>
@@ -1507,7 +1507,7 @@
         <v>-1934.659999999989</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>96232.60000000001</v>
@@ -1553,7 +1553,7 @@
         <v>-1175.720000000007</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>95056.87999999999</v>
